--- a/samples/sensor_hub_SH-100.xlsx
+++ b/samples/sensor_hub_SH-100.xlsx
@@ -526,7 +526,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>W25Q128JVSIQ</t>
+          <t>MX25L12835FM2I-10G</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -534,7 +534,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>128Mbit SPI flash</t>
+          <t>128Mbit SPI NOR flash SOIC-8</t>
         </is>
       </c>
     </row>
